--- a/artfynd/A 765-2023 artfynd.xlsx
+++ b/artfynd/A 765-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1015,6 +1015,462 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>118847543</v>
+      </c>
+      <c r="B5" t="n">
+        <v>90464</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5445</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ekticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fomitiporia robusta</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>A 27067, Stormbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>579181</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6398551</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>118847474</v>
+      </c>
+      <c r="B6" t="n">
+        <v>90464</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5445</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ekticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Fomitiporia robusta</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>A 27067, Stormbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>579164</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6398564</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>118847767</v>
+      </c>
+      <c r="B7" t="n">
+        <v>90464</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5445</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ekticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Fomitiporia robusta</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>A 27067, Stormbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>579192</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6398472</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>118847732</v>
+      </c>
+      <c r="B8" t="n">
+        <v>90464</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5445</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ekticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Fomitiporia robusta</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>A 27067, Stormbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>579209</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6398441</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 765-2023 artfynd.xlsx
+++ b/artfynd/A 765-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1471,6 +1471,462 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>118865677</v>
+      </c>
+      <c r="B9" t="n">
+        <v>90464</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5445</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ekticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Fomitiporia robusta</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>A 27067, Stormbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>579225</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6398552</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>118865796</v>
+      </c>
+      <c r="B10" t="n">
+        <v>90464</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5445</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ekticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Fomitiporia robusta</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>A 27067, Stormbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>579224</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6398565</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>118865749</v>
+      </c>
+      <c r="B11" t="n">
+        <v>90464</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5445</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ekticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Fomitiporia robusta</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>A 27067, Stormbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>579228</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6398560</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>118865685</v>
+      </c>
+      <c r="B12" t="n">
+        <v>90464</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5445</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ekticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Fomitiporia robusta</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>A 27067, Stormbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>579271</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6398517</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 765-2023 artfynd.xlsx
+++ b/artfynd/A 765-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118564416</v>
+        <v>118564349</v>
       </c>
       <c r="B2" t="n">
         <v>90464</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579165</v>
+        <v>579169</v>
       </c>
       <c r="R2" t="n">
-        <v>6398368</v>
+        <v>6398411</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,7 +789,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118564349</v>
+        <v>118564482</v>
       </c>
       <c r="B3" t="n">
         <v>90464</v>
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579169</v>
+        <v>579174</v>
       </c>
       <c r="R3" t="n">
-        <v>6398411</v>
+        <v>6398378</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -903,7 +903,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118564482</v>
+        <v>118564416</v>
       </c>
       <c r="B4" t="n">
         <v>90464</v>
@@ -938,7 +938,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579174</v>
+        <v>579165</v>
       </c>
       <c r="R4" t="n">
-        <v>6398378</v>
+        <v>6398368</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1017,7 +1017,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118847543</v>
+        <v>118847767</v>
       </c>
       <c r="B5" t="n">
         <v>90464</v>
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579181</v>
+        <v>579192</v>
       </c>
       <c r="R5" t="n">
-        <v>6398551</v>
+        <v>6398472</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1245,7 +1245,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118847767</v>
+        <v>118847543</v>
       </c>
       <c r="B7" t="n">
         <v>90464</v>
@@ -1296,10 +1296,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579192</v>
+        <v>579181</v>
       </c>
       <c r="R7" t="n">
-        <v>6398472</v>
+        <v>6398551</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1587,7 +1587,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118865796</v>
+        <v>118865685</v>
       </c>
       <c r="B10" t="n">
         <v>90464</v>
@@ -1622,12 +1622,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579224</v>
+        <v>579271</v>
       </c>
       <c r="R10" t="n">
-        <v>6398565</v>
+        <v>6398517</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118865685</v>
+        <v>118865796</v>
       </c>
       <c r="B12" t="n">
         <v>90464</v>
@@ -1850,12 +1850,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579271</v>
+        <v>579224</v>
       </c>
       <c r="R12" t="n">
-        <v>6398517</v>
+        <v>6398565</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 765-2023 artfynd.xlsx
+++ b/artfynd/A 765-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118564482</v>
+        <v>118564416</v>
       </c>
       <c r="B3" t="n">
         <v>90464</v>
@@ -824,7 +824,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579174</v>
+        <v>579165</v>
       </c>
       <c r="R3" t="n">
-        <v>6398378</v>
+        <v>6398368</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -903,7 +903,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118564416</v>
+        <v>118564482</v>
       </c>
       <c r="B4" t="n">
         <v>90464</v>
@@ -938,7 +938,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579165</v>
+        <v>579174</v>
       </c>
       <c r="R4" t="n">
-        <v>6398368</v>
+        <v>6398378</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1131,7 +1131,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118847474</v>
+        <v>118847543</v>
       </c>
       <c r="B6" t="n">
         <v>90464</v>
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579164</v>
+        <v>579181</v>
       </c>
       <c r="R6" t="n">
-        <v>6398564</v>
+        <v>6398551</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1245,7 +1245,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118847543</v>
+        <v>118847474</v>
       </c>
       <c r="B7" t="n">
         <v>90464</v>
@@ -1296,10 +1296,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579181</v>
+        <v>579164</v>
       </c>
       <c r="R7" t="n">
-        <v>6398551</v>
+        <v>6398564</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1473,7 +1473,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118865677</v>
+        <v>118865685</v>
       </c>
       <c r="B9" t="n">
         <v>90464</v>
@@ -1508,12 +1508,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1524,10 +1524,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579225</v>
+        <v>579271</v>
       </c>
       <c r="R9" t="n">
-        <v>6398552</v>
+        <v>6398517</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1587,7 +1587,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118865685</v>
+        <v>118865796</v>
       </c>
       <c r="B10" t="n">
         <v>90464</v>
@@ -1622,12 +1622,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579271</v>
+        <v>579224</v>
       </c>
       <c r="R10" t="n">
-        <v>6398517</v>
+        <v>6398565</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118865796</v>
+        <v>118865677</v>
       </c>
       <c r="B12" t="n">
         <v>90464</v>
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579224</v>
+        <v>579225</v>
       </c>
       <c r="R12" t="n">
-        <v>6398565</v>
+        <v>6398552</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 765-2023 artfynd.xlsx
+++ b/artfynd/A 765-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118564349</v>
+        <v>118564482</v>
       </c>
       <c r="B2" t="n">
-        <v>90464</v>
+        <v>90471</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579169</v>
+        <v>579174</v>
       </c>
       <c r="R2" t="n">
-        <v>6398411</v>
+        <v>6398378</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -792,7 +792,7 @@
         <v>118564416</v>
       </c>
       <c r="B3" t="n">
-        <v>90464</v>
+        <v>90471</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118564482</v>
+        <v>118564349</v>
       </c>
       <c r="B4" t="n">
-        <v>90464</v>
+        <v>90471</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579174</v>
+        <v>579169</v>
       </c>
       <c r="R4" t="n">
-        <v>6398378</v>
+        <v>6398411</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118847767</v>
+        <v>118847474</v>
       </c>
       <c r="B5" t="n">
-        <v>90464</v>
+        <v>90471</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579192</v>
+        <v>579164</v>
       </c>
       <c r="R5" t="n">
-        <v>6398472</v>
+        <v>6398564</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1131,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118847543</v>
+        <v>118847732</v>
       </c>
       <c r="B6" t="n">
-        <v>90464</v>
+        <v>90471</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579181</v>
+        <v>579209</v>
       </c>
       <c r="R6" t="n">
-        <v>6398551</v>
+        <v>6398441</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1245,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118847474</v>
+        <v>118847767</v>
       </c>
       <c r="B7" t="n">
-        <v>90464</v>
+        <v>90471</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1296,10 +1296,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579164</v>
+        <v>579192</v>
       </c>
       <c r="R7" t="n">
-        <v>6398564</v>
+        <v>6398472</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118847732</v>
+        <v>118847543</v>
       </c>
       <c r="B8" t="n">
-        <v>90464</v>
+        <v>90471</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1410,10 +1410,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579209</v>
+        <v>579181</v>
       </c>
       <c r="R8" t="n">
-        <v>6398441</v>
+        <v>6398551</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1473,10 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118865685</v>
+        <v>118865796</v>
       </c>
       <c r="B9" t="n">
-        <v>90464</v>
+        <v>90471</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1508,12 +1508,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1524,10 +1524,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579271</v>
+        <v>579224</v>
       </c>
       <c r="R9" t="n">
-        <v>6398517</v>
+        <v>6398565</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1587,10 +1587,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118865796</v>
+        <v>118865749</v>
       </c>
       <c r="B10" t="n">
-        <v>90464</v>
+        <v>90471</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1622,12 +1622,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579224</v>
+        <v>579228</v>
       </c>
       <c r="R10" t="n">
-        <v>6398565</v>
+        <v>6398560</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1701,10 +1701,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118865749</v>
+        <v>118865677</v>
       </c>
       <c r="B11" t="n">
-        <v>90464</v>
+        <v>90471</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1736,12 +1736,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579228</v>
+        <v>579225</v>
       </c>
       <c r="R11" t="n">
-        <v>6398560</v>
+        <v>6398552</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1815,10 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118865677</v>
+        <v>118865685</v>
       </c>
       <c r="B12" t="n">
-        <v>90464</v>
+        <v>90471</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1850,12 +1850,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579225</v>
+        <v>579271</v>
       </c>
       <c r="R12" t="n">
-        <v>6398552</v>
+        <v>6398517</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 765-2023 artfynd.xlsx
+++ b/artfynd/A 765-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118564482</v>
+        <v>118564349</v>
       </c>
       <c r="B2" t="n">
         <v>90471</v>
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579174</v>
+        <v>579169</v>
       </c>
       <c r="R2" t="n">
-        <v>6398378</v>
+        <v>6398411</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -903,7 +903,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118564349</v>
+        <v>118564482</v>
       </c>
       <c r="B4" t="n">
         <v>90471</v>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579169</v>
+        <v>579174</v>
       </c>
       <c r="R4" t="n">
-        <v>6398411</v>
+        <v>6398378</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1131,7 +1131,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118847732</v>
+        <v>118847767</v>
       </c>
       <c r="B6" t="n">
         <v>90471</v>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579209</v>
+        <v>579192</v>
       </c>
       <c r="R6" t="n">
-        <v>6398441</v>
+        <v>6398472</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1245,7 +1245,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118847767</v>
+        <v>118847543</v>
       </c>
       <c r="B7" t="n">
         <v>90471</v>
@@ -1296,10 +1296,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579192</v>
+        <v>579181</v>
       </c>
       <c r="R7" t="n">
-        <v>6398472</v>
+        <v>6398551</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1359,7 +1359,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118847543</v>
+        <v>118847732</v>
       </c>
       <c r="B8" t="n">
         <v>90471</v>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1410,10 +1410,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579181</v>
+        <v>579209</v>
       </c>
       <c r="R8" t="n">
-        <v>6398551</v>
+        <v>6398441</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1473,7 +1473,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118865796</v>
+        <v>118865685</v>
       </c>
       <c r="B9" t="n">
         <v>90471</v>
@@ -1508,12 +1508,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1524,10 +1524,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579224</v>
+        <v>579271</v>
       </c>
       <c r="R9" t="n">
-        <v>6398565</v>
+        <v>6398517</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1701,7 +1701,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118865677</v>
+        <v>118865796</v>
       </c>
       <c r="B11" t="n">
         <v>90471</v>
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579225</v>
+        <v>579224</v>
       </c>
       <c r="R11" t="n">
-        <v>6398552</v>
+        <v>6398565</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118865685</v>
+        <v>118865677</v>
       </c>
       <c r="B12" t="n">
         <v>90471</v>
@@ -1850,12 +1850,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579271</v>
+        <v>579225</v>
       </c>
       <c r="R12" t="n">
-        <v>6398517</v>
+        <v>6398552</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 765-2023 artfynd.xlsx
+++ b/artfynd/A 765-2023 artfynd.xlsx
@@ -1929,7 +1929,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119608083</v>
+        <v>119624202</v>
       </c>
       <c r="B13" t="n">
         <v>90522</v>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579306</v>
+        <v>579267</v>
       </c>
       <c r="R13" t="n">
-        <v>6398474</v>
+        <v>6398522</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2010,12 +2010,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2043,10 +2043,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119624186</v>
+        <v>119624097</v>
       </c>
       <c r="B14" t="n">
-        <v>90522</v>
+        <v>57463</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2059,48 +2059,49 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5445</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>A 765, Ankarsrum, Sm</t>
+          <t>A 27067, Stormbo, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579294</v>
+        <v>579120</v>
       </c>
       <c r="R14" t="n">
-        <v>6398468</v>
+        <v>6398550</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2138,7 +2139,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2157,7 +2157,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119624202</v>
+        <v>119608083</v>
       </c>
       <c r="B15" t="n">
         <v>90522</v>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>579267</v>
+        <v>579306</v>
       </c>
       <c r="R15" t="n">
-        <v>6398522</v>
+        <v>6398474</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2238,12 +2238,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2271,10 +2271,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119624097</v>
+        <v>119624186</v>
       </c>
       <c r="B16" t="n">
-        <v>57463</v>
+        <v>90522</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2287,49 +2287,48 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>5445</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>A 27067, Stormbo, Sm</t>
+          <t>A 765, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>579120</v>
+        <v>579294</v>
       </c>
       <c r="R16" t="n">
-        <v>6398550</v>
+        <v>6398468</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2367,6 +2366,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 765-2023 artfynd.xlsx
+++ b/artfynd/A 765-2023 artfynd.xlsx
@@ -1929,7 +1929,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119624202</v>
+        <v>119624186</v>
       </c>
       <c r="B13" t="n">
         <v>90522</v>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579267</v>
+        <v>579294</v>
       </c>
       <c r="R13" t="n">
-        <v>6398522</v>
+        <v>6398468</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2043,10 +2043,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119624097</v>
+        <v>119608083</v>
       </c>
       <c r="B14" t="n">
-        <v>57463</v>
+        <v>90522</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2059,49 +2059,48 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>5445</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>A 27067, Stormbo, Sm</t>
+          <t>A 765, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579120</v>
+        <v>579306</v>
       </c>
       <c r="R14" t="n">
-        <v>6398550</v>
+        <v>6398474</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2125,12 +2124,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2139,6 +2138,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2157,10 +2157,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119608083</v>
+        <v>119624097</v>
       </c>
       <c r="B15" t="n">
-        <v>90522</v>
+        <v>57463</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2173,48 +2173,49 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5445</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>A 765, Ankarsrum, Sm</t>
+          <t>A 27067, Stormbo, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>579306</v>
+        <v>579120</v>
       </c>
       <c r="R15" t="n">
-        <v>6398474</v>
+        <v>6398550</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2238,12 +2239,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2252,7 +2253,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2271,7 +2271,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119624186</v>
+        <v>119624202</v>
       </c>
       <c r="B16" t="n">
         <v>90522</v>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2322,10 +2322,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>579294</v>
+        <v>579267</v>
       </c>
       <c r="R16" t="n">
-        <v>6398468</v>
+        <v>6398522</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
